--- a/ADD-ARTEFACT-XDM/ig/CodeSystem-cs-association-type.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/CodeSystem-cs-association-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-03T13:57:35+00:00</t>
+    <t>2026-07-07T20:41:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ADD-ARTEFACT-XDM/ig/CodeSystem-cs-association-type.xlsx
+++ b/ADD-ARTEFACT-XDM/ig/CodeSystem-cs-association-type.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-07T20:41:51+00:00</t>
+    <t>2026-07-09T18:09:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -150,7 +150,7 @@
     <t>Transformation</t>
   </si>
   <si>
-    <t>Le document source est une transformation du document cible (ex : CDA généré depuis des données propriétaires).</t>
+    <t>Le document source est une transformation du document cible (ex : PDF correspondant au document CDA).</t>
   </si>
 </sst>
 </file>
